--- a/数据表/Goods.xlsx
+++ b/数据表/Goods.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19950" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -43,12 +43,6 @@
     <t>GoodsType</t>
   </si>
   <si>
-    <t>MinPrice</t>
-  </si>
-  <si>
-    <t>MaxPrice</t>
-  </si>
-  <si>
     <t>GoodsTypeId</t>
   </si>
   <si>
@@ -62,12 +56,6 @@
   </si>
   <si>
     <t>商品类型</t>
-  </si>
-  <si>
-    <t>最低价格</t>
-  </si>
-  <si>
-    <t>最高价格</t>
   </si>
   <si>
     <t>商品对应物品Id</t>
@@ -1019,18 +1007,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="15.9090909090909" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5454545454545" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.7272727272727" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3636363636364" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5454545454545" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2727272727273" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1040,10 +1026,8 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1057,146 +1041,98 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2">
-        <v>100</v>
-      </c>
-      <c r="F5" s="2">
-        <v>200</v>
-      </c>
-      <c r="G5" s="2">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:5">
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1">
-        <v>120</v>
-      </c>
-      <c r="F6" s="1">
-        <v>150</v>
-      </c>
-      <c r="G6" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2">
         <v>201</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:5">
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
-        <v>200</v>
-      </c>
-      <c r="F7" s="1">
-        <v>230</v>
-      </c>
-      <c r="G7" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:5">
       <c r="B8" s="1">
         <v>104</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1">
-        <v>210</v>
-      </c>
-      <c r="F8" s="1">
-        <v>250</v>
-      </c>
-      <c r="G8" s="1">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:5">
       <c r="B9" s="1">
         <v>105</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1">
-        <v>80</v>
-      </c>
-      <c r="F9" s="1">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1">
         <v>104</v>
       </c>
     </row>

--- a/数据表/Goods.xlsx
+++ b/数据表/Goods.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -1007,7 +1007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="15.9090909090909" style="1" customWidth="1"/>
@@ -1100,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="2">
-        <v>201</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1134,6 +1134,204 @@
       </c>
       <c r="E9" s="1">
         <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="1">
+        <v>106</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="2">
+        <v>107</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="1">
+        <v>108</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="1">
+        <v>109</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="1">
+        <v>110</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="1">
+        <v>111</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="1">
+        <v>112</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2">
+        <v>113</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="1">
+        <v>114</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="1">
+        <v>115</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="1">
+        <v>116</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="1">
+        <v>117</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="1">
+        <v>118</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="1">
+        <v>119</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="1">
+        <v>120</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="1">
+        <v>121</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="1">
+        <v>122</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="1">
+        <v>123</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Goods.xlsx
+++ b/数据表/Goods.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -1007,7 +1007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="15.9090909090909" style="1" customWidth="1"/>
@@ -1332,6 +1332,17 @@
       </c>
       <c r="E27" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="1">
+        <v>124</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Goods.xlsx
+++ b/数据表/Goods.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="21550" windowHeight="10080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,10 @@
     <t>#</t>
   </si>
   <si>
-    <t>商品表</t>
+    <t>Id</t>
   </si>
   <si>
-    <t>Id</t>
+    <t>列1</t>
   </si>
   <si>
     <t>GoodsType</t>
@@ -49,25 +49,82 @@
     <t>int</t>
   </si>
   <si>
-    <t>商品编号</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>商品编号</t>
+    </r>
   </si>
   <si>
-    <t>策划备注</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>策划备注</t>
+    </r>
   </si>
   <si>
-    <t>商品类型</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>商品类型</t>
+    </r>
   </si>
   <si>
-    <t>商品对应物品Id</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>商品对应物品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Id</t>
+    </r>
   </si>
   <si>
-    <t>道具：药</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具：药</t>
+    </r>
   </si>
   <si>
     <t>Prop</t>
   </si>
   <si>
-    <t>小刀</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小刀</t>
+    </r>
   </si>
   <si>
     <t>Weapon</t>
@@ -83,13 +140,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -234,6 +297,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -556,137 +625,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -694,6 +763,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -748,6 +832,43 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -755,6 +876,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:E28" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E28" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="#" dataDxfId="0"/>
+    <tableColumn id="2" name="Id" dataDxfId="1"/>
+    <tableColumn id="3" name="列1" dataDxfId="2"/>
+    <tableColumn id="4" name="GoodsType" dataDxfId="3"/>
+    <tableColumn id="5" name="GoodsTypeId" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1016,339 +1151,389 @@
     <col min="5" max="5" width="17.2727272727273" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="14.5" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="14.5" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5" spans="1:5">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
+        <v>101</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" spans="1:5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6">
+        <v>102</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:5">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6">
+        <v>103</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:5">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6">
+        <v>104</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6">
+        <v>105</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6">
+        <v>106</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="10" ht="14.5" spans="1:5">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4">
+        <v>107</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" spans="1:5">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6">
+        <v>108</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" spans="1:5">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6">
+        <v>109</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" spans="1:5">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6">
+        <v>110</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" spans="1:5">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6">
+        <v>111</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" spans="1:5">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6">
+        <v>112</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5" spans="1:5">
+      <c r="A16" s="5"/>
+      <c r="B16" s="4">
+        <v>113</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5" spans="1:5">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6">
+        <v>114</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5" spans="1:5">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6">
+        <v>115</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5" spans="1:5">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6">
+        <v>116</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5" spans="1:5">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6">
+        <v>117</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5" spans="1:5">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6">
+        <v>118</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5" spans="1:5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6">
+        <v>119</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5" spans="1:5">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6">
+        <v>120</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5" spans="1:5">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6">
+        <v>121</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" ht="14.5" spans="1:5">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6">
+        <v>122</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" ht="14.5" spans="1:5">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6">
+        <v>123</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="6">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="27" ht="14.5" spans="1:5">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6">
+        <v>124</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
-        <v>101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" s="1">
-        <v>102</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" s="1">
-        <v>103</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="1">
-        <v>104</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="1">
-        <v>105</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" s="1">
-        <v>106</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" s="2">
-        <v>107</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12" s="1">
-        <v>108</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="1">
-        <v>109</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="1">
-        <v>110</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="1">
-        <v>111</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="1">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="B16" s="1">
-        <v>112</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="2">
-        <v>113</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="1">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="1">
-        <v>114</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="1">
-        <v>115</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="1">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="1">
-        <v>116</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="1">
-        <v>117</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="1">
-        <v>118</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="1">
-        <v>119</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="1">
-        <v>120</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="1">
-        <v>121</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="1">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="1">
-        <v>122</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="1">
-        <v>123</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="1:5">
       <c r="B28" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
